--- a/ExcelTool/LubanTools/DataTables/Datas/QuestDataConfig.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/QuestDataConfig.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D990D65-AA95-4BFA-8A9C-351954208905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E63CDB-4ED8-452E-BC4B-62EBF6468486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,17 @@
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1786007739" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1786007739" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1786007739" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1786007739"/>
+      <pm:revision xmlns:pm="smNativeData" day="1786331838" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1786331838" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1786331838" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1786331838"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -39,6 +39,9 @@
     <t>Remark</t>
   </si>
   <si>
+    <t>QuestTrigger</t>
+  </si>
+  <si>
     <t>AcceptCond</t>
   </si>
   <si>
@@ -48,178 +51,157 @@
     <t>DescKey</t>
   </si>
   <si>
+    <t>IconKey</t>
+  </si>
+  <si>
     <t>QuestObjData</t>
   </si>
   <si>
+    <t>Reward</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>领取方式</t>
+  </si>
+  <si>
+    <t>接受条件</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>文本</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
+    <t>任务目标</t>
+  </si>
+  <si>
+    <t>任务奖励</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>测试任务1</t>
+  </si>
+  <si>
+    <t>EnterZone:101</t>
+  </si>
+  <si>
+    <t>TestQuest1Name</t>
+  </si>
+  <si>
+    <t>TestQuest1Desc</t>
+  </si>
+  <si>
+    <t>TestQuest1Icon</t>
+  </si>
+  <si>
+    <t>10001+10002</t>
+  </si>
+  <si>
+    <t>Coin:100/Affection:10001:10</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>测试任务2</t>
+  </si>
+  <si>
+    <t>ExitZone:101</t>
+  </si>
+  <si>
+    <t>TestQuest2Name</t>
+  </si>
+  <si>
+    <t>TestQuest2Desc</t>
+  </si>
+  <si>
+    <t>TestQuest2Icon</t>
+  </si>
+  <si>
+    <t>10001+10002+10003</t>
+  </si>
+  <si>
+    <t>Item:100001:1</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>测试任务3</t>
+  </si>
+  <si>
+    <t>ClickNpc:10001</t>
+  </si>
+  <si>
+    <t>TestQuest3Name</t>
+  </si>
+  <si>
+    <t>TestQuest3Desc</t>
+  </si>
+  <si>
+    <t>TestQuest3Icon</t>
+  </si>
+  <si>
+    <t>10004</t>
+  </si>
+  <si>
+    <t>测试任务4</t>
+  </si>
+  <si>
+    <t>EnterZoneStay:101:5</t>
+  </si>
+  <si>
+    <t>TestQuest4Name</t>
+  </si>
+  <si>
+    <t>TestQuest4Desc</t>
+  </si>
+  <si>
+    <t>TestQuest4Icon</t>
+  </si>
+  <si>
+    <t>10002+10005</t>
+  </si>
+  <si>
+    <t>Coin:100</t>
+  </si>
+  <si>
+    <t>10005</t>
+  </si>
+  <si>
+    <t>测试任务5</t>
+  </si>
+  <si>
+    <t>DialogNpc:10001</t>
+  </si>
+  <si>
+    <t>TestQuest5Name</t>
+  </si>
+  <si>
+    <t>TestQuest5Desc</t>
+  </si>
+  <si>
+    <t>TestQuest5Icon</t>
+  </si>
+  <si>
     <t>long</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>任务名称</t>
-  </si>
-  <si>
-    <t>TestQuest1Name</t>
-  </si>
-  <si>
-    <t>TestQuest2Name</t>
-  </si>
-  <si>
-    <t>TestQuest3Name</t>
-  </si>
-  <si>
-    <t>TestQuest4Name</t>
-  </si>
-  <si>
-    <t>TestQuest5Name</t>
-  </si>
-  <si>
-    <t>AcceptTrigger</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>ExtraQuestObjData</t>
-  </si>
-  <si>
-    <t>领取条件ID</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>10001</t>
-  </si>
-  <si>
-    <t>10002</t>
-  </si>
-  <si>
-    <t>10003</t>
-  </si>
-  <si>
-    <t>10004</t>
-  </si>
-  <si>
-    <t>10005</t>
-  </si>
-  <si>
-    <t>领取触发 类型:参数:参数，多条用 / 分隔</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务目标 类型:参数:参数，多条用 / 分隔</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>超额目标 类型:参数:参数，多条用 / 分隔</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnterZone:101</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>DayPassed:2/CompleteGame:1001:2:0</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>CompleteGame:1001:2:1</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExitZone:101</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>DayPassed:2/CompleteGame:1001:2:1/Dialog:10001</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialog:10002</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClickNpc:10001</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>GiveGift:10001:100001:1</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnterZoneStay:101:5</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>CompleteQuest:10001</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>DialogNpc:10001</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuyItem:100001:1/HoldItem:100001:2</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务文本</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试任务1</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>TestQuest1Desc</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试任务2</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>TestQuest2Desc</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试任务3</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>TestQuest3Desc</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试任务4</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>TestQuest4Desc</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试任务5</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>TestQuest5Desc</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -227,28 +209,20 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>ExtraReward</t>
+    <t>(list#sep=+),long</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>Item:100001:1</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励 Item:道具ID[:数量] / 属性名:数值 / 角色属性名:NPC ID:数值，多条用 / 分隔</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>超额奖励 写法同奖励列</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin:100/Goodwill:10001:10</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin:100</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <t>ObjInOrder</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>目标是否按顺序完成</t>
+  </si>
+  <si>
+    <t>False</t>
   </si>
 </sst>
 </file>
@@ -273,7 +247,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -281,14 +254,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -296,7 +267,6 @@
       <sz val="18"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -304,7 +274,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -312,7 +281,6 @@
       <sz val="15"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -320,7 +288,6 @@
       <sz val="13"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -328,14 +295,12 @@
       <sz val="11"/>
       <color rgb="FF44546A"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -343,7 +308,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -351,7 +315,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -359,14 +322,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -374,48 +335,41 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1154,10 +1108,10 @@
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1786007739" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1786331838" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1786007739" count="43">
+      <pm:colors xmlns:pm="smNativeData" id="1786331838" count="41">
         <pm:color name="颜色 24" rgb="800080"/>
         <pm:color name="颜色 25" rgb="44546A"/>
         <pm:color name="颜色 26" rgb="3F3F76"/>
@@ -1166,41 +1120,39 @@
         <pm:color name="颜色 29" rgb="006100"/>
         <pm:color name="颜色 30" rgb="9C0006"/>
         <pm:color name="颜色 31" rgb="9C6500"/>
-        <pm:color name="颜色 32" rgb="ED7D31"/>
-        <pm:color name="20% 灰色" rgb="000000"/>
-        <pm:color name="颜色 34" rgb="5B9BD5"/>
-        <pm:color name="颜色 35" rgb="70AD47"/>
-        <pm:color name="颜色 36" rgb="ACB9CA"/>
-        <pm:color name="颜色 37" rgb="FFFFCC"/>
-        <pm:color name="颜色 38" rgb="FFCC99"/>
-        <pm:color name="颜色 39" rgb="F2F2F2"/>
-        <pm:color name="颜色 40" rgb="A5A5A5"/>
-        <pm:color name="颜色 41" rgb="C6EFCE"/>
-        <pm:color name="颜色 42" rgb="FFC7CE"/>
-        <pm:color name="颜色 43" rgb="FFEB9C"/>
-        <pm:color name="颜色 44" rgb="DDEBF7"/>
-        <pm:color name="颜色 45" rgb="BDD7EE"/>
-        <pm:color name="颜色 46" rgb="9BC2E6"/>
-        <pm:color name="颜色 47" rgb="FBE3D5"/>
-        <pm:color name="颜色 48" rgb="F8CAAB"/>
-        <pm:color name="颜色 49" rgb="F4AF82"/>
-        <pm:color name="颜色 50" rgb="EBEBEB"/>
-        <pm:color name="颜色 51" rgb="D9D9D9"/>
-        <pm:color name="颜色 52" rgb="C7C7C7"/>
-        <pm:color name="颜色 53" rgb="FFC000"/>
-        <pm:color name="颜色 54" rgb="FFF2CA"/>
-        <pm:color name="颜色 55" rgb="FFE697"/>
-        <pm:color name="颜色 56" rgb="FFD964"/>
-        <pm:color name="颜色 57" rgb="4472C4"/>
-        <pm:color name="颜色 58" rgb="D9E1F2"/>
-        <pm:color name="颜色 59" rgb="B4C6E7"/>
-        <pm:color name="颜色 60" rgb="8EA9DB"/>
-        <pm:color name="颜色 61" rgb="E1EFD8"/>
-        <pm:color name="颜色 62" rgb="C5DFB3"/>
-        <pm:color name="颜色 63" rgb="A8D08C"/>
-        <pm:color name="颜色 64" rgb="B2B2B2"/>
-        <pm:color name="颜色 65" rgb="ACCCEA"/>
-        <pm:color name="颜色 66" rgb="FF8001"/>
+        <pm:color name="颜色 32" rgb="FFFFCC"/>
+        <pm:color name="颜色 33" rgb="FFCC99"/>
+        <pm:color name="颜色 34" rgb="F2F2F2"/>
+        <pm:color name="颜色 35" rgb="A5A5A5"/>
+        <pm:color name="颜色 36" rgb="C6EFCE"/>
+        <pm:color name="颜色 37" rgb="FFC7CE"/>
+        <pm:color name="颜色 38" rgb="FFEB9C"/>
+        <pm:color name="颜色 39" rgb="5B9BD5"/>
+        <pm:color name="颜色 40" rgb="DDEBF7"/>
+        <pm:color name="颜色 41" rgb="BDD7EE"/>
+        <pm:color name="颜色 42" rgb="9BC2E6"/>
+        <pm:color name="颜色 43" rgb="ED7D31"/>
+        <pm:color name="颜色 44" rgb="FBE3D5"/>
+        <pm:color name="颜色 45" rgb="F8CAAB"/>
+        <pm:color name="颜色 46" rgb="F4AF82"/>
+        <pm:color name="颜色 47" rgb="EBEBEB"/>
+        <pm:color name="颜色 48" rgb="D9D9D9"/>
+        <pm:color name="颜色 49" rgb="C7C7C7"/>
+        <pm:color name="颜色 50" rgb="FFC000"/>
+        <pm:color name="颜色 51" rgb="FFF2CA"/>
+        <pm:color name="颜色 52" rgb="FFE697"/>
+        <pm:color name="颜色 53" rgb="FFD964"/>
+        <pm:color name="颜色 54" rgb="4472C4"/>
+        <pm:color name="颜色 55" rgb="D9E1F2"/>
+        <pm:color name="颜色 56" rgb="B4C6E7"/>
+        <pm:color name="颜色 57" rgb="8EA9DB"/>
+        <pm:color name="颜色 58" rgb="70AD47"/>
+        <pm:color name="颜色 59" rgb="E1EFD8"/>
+        <pm:color name="颜色 60" rgb="C5DFB3"/>
+        <pm:color name="颜色 61" rgb="A8D08C"/>
+        <pm:color name="颜色 62" rgb="B2B2B2"/>
+        <pm:color name="颜色 63" rgb="ACCCEA"/>
+        <pm:color name="颜色 64" rgb="FF8001"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -1464,18 +1416,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="28.58203125" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="26.08203125" customWidth="1"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1"/>
+    <col min="5" max="5" width="11.08203125" customWidth="1"/>
     <col min="6" max="6" width="21.25" customWidth="1"/>
     <col min="7" max="7" width="20.25" customWidth="1"/>
-    <col min="8" max="8" width="33.1640625" customWidth="1"/>
-    <col min="9" max="9" width="38.08203125" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1489,156 +1439,156 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>34</v>
@@ -1647,115 +1597,115 @@
         <v>35</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1764,7 +1714,7 @@
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1786007739" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1786331838" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/ExcelTool/LubanTools/DataTables/Datas/QuestDataConfig.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/QuestDataConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E63CDB-4ED8-452E-BC4B-62EBF6468486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8F9339-6527-40A8-BC9D-25BEA26D3A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,17 +18,17 @@
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1786331838" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1786331838" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1786331838" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1786331838"/>
+      <pm:revision xmlns:pm="smNativeData" day="1786440206" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1786440206" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1786440206" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1786440206"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -60,16 +60,31 @@
     <t>Reward</t>
   </si>
   <si>
+    <t>ObjInOrder</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>领取方式</t>
+    <t>接受方式</t>
   </si>
   <si>
     <t>接受条件</t>
@@ -90,6 +105,9 @@
     <t>任务奖励</t>
   </si>
   <si>
+    <t>目标是否按顺序完成</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -99,9 +117,6 @@
     <t>测试任务1</t>
   </si>
   <si>
-    <t>EnterZone:101</t>
-  </si>
-  <si>
     <t>TestQuest1Name</t>
   </si>
   <si>
@@ -117,15 +132,15 @@
     <t>Coin:100/Affection:10001:10</t>
   </si>
   <si>
+    <t>False</t>
+  </si>
+  <si>
     <t>10002</t>
   </si>
   <si>
     <t>测试任务2</t>
   </si>
   <si>
-    <t>ExitZone:101</t>
-  </si>
-  <si>
     <t>TestQuest2Name</t>
   </si>
   <si>
@@ -165,9 +180,6 @@
     <t>测试任务4</t>
   </si>
   <si>
-    <t>EnterZoneStay:101:5</t>
-  </si>
-  <si>
     <t>TestQuest4Name</t>
   </si>
   <si>
@@ -201,28 +213,16 @@
     <t>TestQuest5Icon</t>
   </si>
   <si>
-    <t>long</t>
+    <t>EnterZone:10000:10001</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
+    <t>ExitZone:10000:10001</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>(list#sep=+),long</t>
+    <t>EnterZoneStay:10000:10001:5</t>
     <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>ObjInOrder</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>目标是否按顺序完成</t>
-  </si>
-  <si>
-    <t>False</t>
   </si>
 </sst>
 </file>
@@ -1108,10 +1108,10 @@
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1786331838" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1786440206" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1786331838" count="41">
+      <pm:colors xmlns:pm="smNativeData" id="1786440206" count="41">
         <pm:color name="颜色 24" rgb="800080"/>
         <pm:color name="颜色 25" rgb="44546A"/>
         <pm:color name="颜色 26" rgb="3F3F76"/>
@@ -1418,8 +1418,8 @@
   <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="28.58203125" customWidth="1"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1"/>
+    <col min="3" max="3" width="15.58203125" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" customWidth="1"/>
     <col min="5" max="5" width="11.08203125" customWidth="1"/>
     <col min="6" max="6" width="21.25" customWidth="1"/>
     <col min="7" max="7" width="20.25" customWidth="1"/>
@@ -1460,252 +1460,252 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
+      </c>
+      <c r="E4" s="1">
+        <v>10002</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>62</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10003</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>44</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10004</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>63</v>
+      </c>
+      <c r="E7" s="1">
+        <v>10006</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10005</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1714,7 +1714,7 @@
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1786331838" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1786440206" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
